--- a/Compititor's_Price/Novia_Prices/Novia_Prices_28-10-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_28-10-2026.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£84.66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£137.24</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>£124.94</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£134.56</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
